--- a/results/04_final_refined_daily_hydroclimate_data/601/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Min_Temperature_timeseries.xlsx
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -792,7 +792,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
